--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.88249016186262</v>
+        <v>12.00590465130268</v>
       </c>
       <c r="D2" t="n">
-        <v>75.01629485299335</v>
+        <v>12.19014791361142</v>
       </c>
       <c r="E2" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F2" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.20846395864112</v>
+        <v>10.43387539327918</v>
       </c>
       <c r="D3" t="n">
-        <v>65.50582007485195</v>
+        <v>10.64469576216344</v>
       </c>
       <c r="E3" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F3" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.93944011378181</v>
+        <v>7.627659018489545</v>
       </c>
       <c r="D4" t="n">
-        <v>48.19452413447813</v>
+        <v>7.831610171852696</v>
       </c>
       <c r="E4" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F4" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.44110977146931</v>
+        <v>7.546680337863764</v>
       </c>
       <c r="D5" t="n">
-        <v>46.31044350545661</v>
+        <v>7.5254470696367</v>
       </c>
       <c r="E5" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F5" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.58538959374595</v>
+        <v>5.457625808983718</v>
       </c>
       <c r="D6" t="n">
-        <v>34.58852863784948</v>
+        <v>5.62063590365054</v>
       </c>
       <c r="E6" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F6" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.16931754662161</v>
+        <v>7.502514101326012</v>
       </c>
       <c r="D7" t="n">
-        <v>47.52571622633005</v>
+        <v>7.722928886778634</v>
       </c>
       <c r="E7" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F7" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.46366534223538</v>
+        <v>6.25034561811325</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80296358368489</v>
+        <v>6.467981582348794</v>
       </c>
       <c r="E8" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F8" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44168188593692</v>
+        <v>2.02177330646475</v>
       </c>
       <c r="D9" t="n">
-        <v>13.79713046621522</v>
+        <v>2.242033700759974</v>
       </c>
       <c r="E9" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F9" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.83117032863579</v>
+        <v>8.097565178403315</v>
       </c>
       <c r="D10" t="n">
-        <v>50.97023286401291</v>
+        <v>8.282662840402098</v>
       </c>
       <c r="E10" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F10" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.26205075212509</v>
+        <v>5.730083247220327</v>
       </c>
       <c r="D11" t="n">
-        <v>36.41168352818806</v>
+        <v>5.91689857333056</v>
       </c>
       <c r="E11" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F11" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.12989363473972</v>
+        <v>6.033607715645204</v>
       </c>
       <c r="D12" t="n">
-        <v>36.15323778431397</v>
+        <v>5.87490113995102</v>
       </c>
       <c r="E12" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F12" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.80255162159834</v>
+        <v>6.142914638509731</v>
       </c>
       <c r="D13" t="n">
-        <v>38.42516376810892</v>
+        <v>6.244089112317701</v>
       </c>
       <c r="E13" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F13" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>42.62573304476765</v>
+        <v>6.926681619774743</v>
       </c>
       <c r="D14" t="n">
-        <v>42.97607869468251</v>
+        <v>6.983612787885908</v>
       </c>
       <c r="E14" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F14" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.72616326098254</v>
+        <v>8.243001529909662</v>
       </c>
       <c r="D15" t="n">
-        <v>50.99010848379307</v>
+        <v>8.285892628616375</v>
       </c>
       <c r="E15" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F15" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>38.51185082169353</v>
+        <v>6.258175758525199</v>
       </c>
       <c r="D16" t="n">
-        <v>38.30496481968815</v>
+        <v>6.224556783199325</v>
       </c>
       <c r="E16" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F16" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>55.84555676943791</v>
+        <v>9.074902975033661</v>
       </c>
       <c r="D17" t="n">
-        <v>55.88958202057051</v>
+        <v>9.082057078342707</v>
       </c>
       <c r="E17" t="n">
-        <v>13.38625683309684</v>
+        <v>2.175266735378236</v>
       </c>
       <c r="F17" t="n">
-        <v>13.42346193522389</v>
+        <v>2.181312564473882</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
